--- a/情报/西安房价爬虫/西安房价数据_真实来源.xlsx
+++ b/情报/西安房价爬虫/西安房价数据_真实来源.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-15T12:24:07.006435</t>
+          <t>2026-05-15T12:31:01.462075</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-15T12:24:07.006435</t>
+          <t>2026-05-15T12:31:01.462075</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-15T12:24:07.006435</t>
+          <t>2026-05-15T12:31:01.462075</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-15T12:24:07.006435</t>
+          <t>2026-05-15T12:31:01.462075</t>
         </is>
       </c>
     </row>
@@ -550,17 +550,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>住宅网签套数</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>住宅网签套数</t>
+          <t>网签面积(万㎡)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>网签总面积(万㎡)</t>
+          <t>来源媒体</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -575,16 +575,20 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>8643</v>
+      </c>
       <c r="C2" t="n">
-        <v>8643</v>
-      </c>
-      <c r="D2" t="n">
         <v>90.09</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>搜狐/乐居买房</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://m.jiemian.com/article/14220278.html</t>
+          <t>https://www.sohu.com/a/983971253_804292</t>
         </is>
       </c>
     </row>
@@ -594,16 +598,20 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>4859</v>
+      </c>
       <c r="C3" t="n">
-        <v>4859</v>
-      </c>
-      <c r="D3" t="n">
         <v>50.63</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>搜狐/乐居买房</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://m.jiemian.com/article/14220278.html</t>
+          <t>https://www.sohu.com/a/993267775_804292</t>
         </is>
       </c>
     </row>
@@ -613,12 +621,16 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>11288</v>
+      </c>
       <c r="C4" t="n">
-        <v>11288</v>
-      </c>
-      <c r="D4" t="n">
         <v>115.11</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>界面新闻</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -632,16 +644,20 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>11903</v>
+      </c>
       <c r="C5" t="n">
-        <v>11903</v>
-      </c>
-      <c r="D5" t="n">
         <v>122.6</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>搜狐/乐居买房</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1005026339_220260</t>
+          <t>https://www.sohu.com/a/1019885202_220260</t>
         </is>
       </c>
     </row>
